--- a/SNH48成员名单生日表2603.xlsx
+++ b/SNH48成员名单生日表2603.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="4" r:id="Rf01ee403813940a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="4" r:id="R804523e2c8ba443b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14509,13 +14509,13 @@
         <x:v>473</x:v>
       </x:c>
       <x:c r="D449" s="5" t="n">
-        <x:v>36837</x:v>
+        <x:v>35741</x:v>
       </x:c>
       <x:c r="E449" s="5">
         <x:v>43210</x:v>
       </x:c>
       <x:c r="F449" s="1" t="n">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G449" s="1" t="n">
         <x:v>164</x:v>
